--- a/Min_Diagramportal/data_pipeline/mal_och_prognoser.xlsx
+++ b/Min_Diagramportal/data_pipeline/mal_och_prognoser.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\SR-Disk-2\Hem0006\jimlin\Desktop\Mina_Befolknings_Dashboards\Min_Diagramportal\data_pipeline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61F5F25B-AFEF-4B7A-B1F0-FD4D1F0F5119}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42E636E1-9E23-4836-86B0-032456C637B0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17505" activeTab="1" xr2:uid="{667748E1-8596-4103-B17E-56D7005BF702}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17505" xr2:uid="{667748E1-8596-4103-B17E-56D7005BF702}"/>
   </bookViews>
   <sheets>
     <sheet name="Befolkningsförändringar" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1156" uniqueCount="64">
   <si>
     <t>Befolkningsförändring_Prognos</t>
   </si>
@@ -577,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5088469-275E-48ED-9E68-C4E7FD82D6F9}">
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="29.42578125" bestFit="1" customWidth="1"/>
@@ -2670,6 +2670,38 @@
         <v>168780</v>
       </c>
     </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>2026</v>
+      </c>
+      <c r="B66">
+        <v>1</v>
+      </c>
+      <c r="C66">
+        <v>710</v>
+      </c>
+      <c r="D66">
+        <v>1510</v>
+      </c>
+      <c r="E66">
+        <v>1290</v>
+      </c>
+      <c r="F66">
+        <v>9940</v>
+      </c>
+      <c r="G66" t="s">
+        <v>7</v>
+      </c>
+      <c r="H66">
+        <v>9450</v>
+      </c>
+      <c r="I66" t="s">
+        <v>7</v>
+      </c>
+      <c r="J66">
+        <v>169420</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2677,7 +2709,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1554125D-35C7-4035-8CB1-7D5ADFD973FE}">
-  <dimension ref="A1:AE25"/>
+  <dimension ref="A1:AE26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
@@ -5017,6 +5049,98 @@
         <v>7</v>
       </c>
     </row>
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2026</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" t="s">
+        <v>7</v>
+      </c>
+      <c r="G26" t="s">
+        <v>7</v>
+      </c>
+      <c r="H26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I26" t="s">
+        <v>7</v>
+      </c>
+      <c r="J26" t="s">
+        <v>7</v>
+      </c>
+      <c r="K26" t="s">
+        <v>7</v>
+      </c>
+      <c r="L26" t="s">
+        <v>7</v>
+      </c>
+      <c r="M26" t="s">
+        <v>7</v>
+      </c>
+      <c r="N26" t="s">
+        <v>7</v>
+      </c>
+      <c r="O26" t="s">
+        <v>7</v>
+      </c>
+      <c r="P26" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>7</v>
+      </c>
+      <c r="R26" t="s">
+        <v>7</v>
+      </c>
+      <c r="S26" t="s">
+        <v>7</v>
+      </c>
+      <c r="T26" t="s">
+        <v>7</v>
+      </c>
+      <c r="U26" t="s">
+        <v>7</v>
+      </c>
+      <c r="V26" t="s">
+        <v>7</v>
+      </c>
+      <c r="W26" t="s">
+        <v>7</v>
+      </c>
+      <c r="X26" t="s">
+        <v>7</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>7</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA26" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>7</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>7</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5024,7 +5148,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D908CB21-F5B0-4B44-9D7F-366C4D3FED9C}">
-  <dimension ref="A1:N65"/>
+  <dimension ref="A1:N66"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -7885,6 +8009,14 @@
       </c>
       <c r="N65" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>2026</v>
+      </c>
+      <c r="B66">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7894,7 +8026,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CAE6402-BB72-4450-A30C-4FE54FE3E432}">
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="29" bestFit="1" customWidth="1"/>
@@ -9002,6 +9134,14 @@
         <v>42.539929879236468</v>
       </c>
     </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>2026</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
